--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484723_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484723_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.2465</v>
+        <v>2.1061</v>
       </c>
       <c r="E2" t="n">
-        <v>0.783</v>
+        <v>1.1929</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4634</v>
+        <v>0.9132</v>
       </c>
       <c r="G2" t="n">
         <v>3.6821</v>
@@ -610,13 +610,13 @@
         <v>2.6418</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.1751</v>
+        <v>-1.3155</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.4697</v>
+        <v>-1.0598</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7054</v>
+        <v>-0.2556</v>
       </c>
       <c r="V2" t="n">
         <v>1.0603</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8361</v>
+        <v>0.9336</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.4934</v>
+        <v>-0.396</v>
       </c>
       <c r="F3" t="n">
         <v>1.3295</v>
@@ -688,10 +688,10 @@
         <v>1.1322</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9558</v>
+        <v>-0.8584000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7642</v>
+        <v>-0.6667999999999999</v>
       </c>
       <c r="U3" t="n">
         <v>-0.1916</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2313</v>
+        <v>-0.2049</v>
       </c>
       <c r="E4" t="n">
         <v>-0.0964</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1349</v>
+        <v>-0.1084</v>
       </c>
       <c r="G4" t="n">
         <v>-0.0603</v>
@@ -766,13 +766,13 @@
         <v>0.1887</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3598</v>
+        <v>-0.3333</v>
       </c>
       <c r="T4" t="n">
         <v>-0.1176</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2422</v>
+        <v>-0.2157</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5767</v>
+        <v>-0.9908</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0419</v>
+        <v>-0.4251</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6186</v>
+        <v>-0.5657</v>
       </c>
       <c r="G5" t="n">
         <v>-1.8583</v>
@@ -844,13 +844,13 @@
         <v>0.9435</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2022</v>
+        <v>-0.2119</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5349</v>
+        <v>0.0679</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3327</v>
+        <v>-0.2798</v>
       </c>
       <c r="V5" t="n">
         <v>0.1359</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. AJAYI</t>
+          <t>M. PEREZ MARCO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1056</v>
+        <v>-1.724</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.0449</v>
+        <v>-0.8945</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9393</v>
+        <v>-0.8295</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.9733</v>
+        <v>0.4794</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.6638</v>
+        <v>0.3083</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3095</v>
+        <v>0.171</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0221</v>
+        <v>0.0411</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.036</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0582</v>
+        <v>0.0411</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.9954</v>
+        <v>0.4383</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.6278</v>
+        <v>0.3083</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3676</v>
+        <v>0.1299</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7548</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.0757</v>
+        <v>-0.9435</v>
       </c>
       <c r="R6" t="n">
-        <v>2.8305</v>
+        <v>0.1887</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1129</v>
+        <v>-0.2034</v>
       </c>
       <c r="T6" t="n">
-        <v>0.008699999999999999</v>
+        <v>-0.2939</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1042</v>
+        <v>0.0905</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. NAVARRO MORALES</t>
+          <t>F. AJAYI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.8561</v>
+        <v>-1.9199</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.4224</v>
+        <v>-2.7269</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5663</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4274</v>
+        <v>-1.9733</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1745</v>
+        <v>-1.6638</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6019</v>
+        <v>-0.3095</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1034</v>
+        <v>0.0221</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0211</v>
+        <v>-0.036</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0823</v>
+        <v>0.0582</v>
       </c>
       <c r="M7" t="n">
-        <v>0.324</v>
+        <v>-1.9954</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1956</v>
+        <v>-1.6278</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5196</v>
+        <v>-0.3676</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.2644</v>
+        <v>0.7548</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.8305</v>
+        <v>-2.0757</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5661</v>
+        <v>2.8305</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1658</v>
+        <v>-0.7015</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0029</v>
+        <v>-0.6733</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1629</v>
+        <v>-0.0281</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1849</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.4867</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. PEREZ MARCO</t>
+          <t>J. NAVARRO MORALES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8563</v>
+        <v>-2.1812</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8945</v>
+        <v>-2.6946</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9618</v>
+        <v>0.5134</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4794</v>
+        <v>0.4274</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3083</v>
+        <v>-0.1745</v>
       </c>
       <c r="I8" t="n">
-        <v>0.171</v>
+        <v>0.6019</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0411</v>
+        <v>0.1034</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.0211</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0411</v>
+        <v>0.0823</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4383</v>
+        <v>0.324</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3083</v>
+        <v>-0.1956</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1299</v>
+        <v>0.5196</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7548</v>
+        <v>-2.2644</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9435</v>
+        <v>-2.8305</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1887</v>
+        <v>0.5661</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3357</v>
+        <v>-0.1593</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2939</v>
+        <v>-0.2693</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0417</v>
+        <v>0.11</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2452</v>
+        <v>-0.1849</v>
       </c>
       <c r="W8" t="n">
         <v>0.3018</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.547</v>
+        <v>-0.4867</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.9469</v>
+        <v>-2.9373</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.747</v>
+        <v>-3.5522</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8001</v>
+        <v>0.6149</v>
       </c>
       <c r="G9" t="n">
         <v>-2.7277</v>
@@ -1156,13 +1156,13 @@
         <v>1.6983</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0306</v>
+        <v>-0.0209</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5262</v>
+        <v>-0.3313</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4956</v>
+        <v>0.3105</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2345</v>
+        <v>-2.9422</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9529</v>
+        <v>-0.6606</v>
       </c>
       <c r="F10" t="n">
         <v>-2.2816</v>
@@ -1234,10 +1234,10 @@
         <v>1.5096</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7083</v>
+        <v>-0.416</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7055</v>
+        <v>-0.4131</v>
       </c>
       <c r="U10" t="n">
         <v>-0.0029</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7333</v>
+        <v>-3.4674</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1778</v>
+        <v>-0.8854</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.5555</v>
+        <v>-2.582</v>
       </c>
       <c r="G11" t="n">
         <v>-0.9211</v>
@@ -1312,13 +1312,13 @@
         <v>1.1322</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8312</v>
+        <v>-0.5654</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.3544</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1846</v>
+        <v>-0.211</v>
       </c>
       <c r="V11" t="n">
         <v>-2.1696</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.3423</v>
+        <v>-5.1524</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.3744</v>
+        <v>-3.8671</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9679</v>
+        <v>-1.2854</v>
       </c>
       <c r="G12" t="n">
         <v>-2.8945</v>
@@ -1390,13 +1390,13 @@
         <v>2.2644</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0576</v>
+        <v>0.2475</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7026</v>
+        <v>-0.1952</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7602</v>
+        <v>0.4427</v>
       </c>
       <c r="V12" t="n">
         <v>-3.6377</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.7814</v>
+        <v>-6.5135</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.9594</v>
+        <v>-5.7444</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.822</v>
+        <v>-0.7691</v>
       </c>
       <c r="G13" t="n">
         <v>-3.0171</v>
@@ -1468,13 +1468,13 @@
         <v>0.9435</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4474</v>
+        <v>-0.1794</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6438</v>
+        <v>-0.4288</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1964</v>
+        <v>0.2493</v>
       </c>
       <c r="V13" t="n">
         <v>-2.3735</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-25.5818</v>
+        <v>-24.9939</v>
       </c>
       <c r="E14" t="n">
-        <v>-21.3382</v>
+        <v>-20.7503</v>
       </c>
       <c r="F14" t="n">
         <v>-4.2437</v>
@@ -1546,13 +1546,13 @@
         <v>16.0395</v>
       </c>
       <c r="S14" t="n">
-        <v>-5.305400000000001</v>
+        <v>-4.717500000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-5.323700000000001</v>
+        <v>-4.7356</v>
       </c>
       <c r="U14" t="n">
-        <v>0.01819999999999997</v>
+        <v>0.01830000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-7.452300000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.6794</v>
+        <v>6.4491</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0206</v>
+        <v>3.6052</v>
       </c>
       <c r="F15" t="n">
-        <v>2.6588</v>
+        <v>2.844</v>
       </c>
       <c r="G15" t="n">
         <v>2.3908</v>
@@ -1624,13 +1624,13 @@
         <v>1.5096</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3715</v>
+        <v>0.3983</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8107</v>
+        <v>-0.2261</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4392</v>
+        <v>0.6243</v>
       </c>
       <c r="V15" t="n">
         <v>3.094</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.0828</v>
+        <v>5.3918</v>
       </c>
       <c r="E16" t="n">
-        <v>3.2537</v>
+        <v>3.3512</v>
       </c>
       <c r="F16" t="n">
-        <v>1.829</v>
+        <v>2.0407</v>
       </c>
       <c r="G16" t="n">
         <v>1.1812</v>
@@ -1702,13 +1702,13 @@
         <v>1.6983</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3545</v>
+        <v>0.6635</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1023</v>
+        <v>-0.0049</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4568</v>
+        <v>0.6684</v>
       </c>
       <c r="V16" t="n">
         <v>1.8488</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V. SANTAMATILDE PERIS</t>
+          <t>P. LUENGO MATEO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.4987</v>
+        <v>4.0865</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0594</v>
+        <v>2.8074</v>
       </c>
       <c r="F17" t="n">
-        <v>3.4393</v>
+        <v>1.2791</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0913</v>
+        <v>2.4542</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1471</v>
+        <v>0.3827</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2384</v>
+        <v>2.0715</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9360000000000001</v>
+        <v>3.8211</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8452</v>
+        <v>1.9447</v>
       </c>
       <c r="L17" t="n">
-        <v>0.09080000000000001</v>
+        <v>1.8764</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1553</v>
+        <v>-1.3669</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9923</v>
+        <v>-1.562</v>
       </c>
       <c r="O17" t="n">
-        <v>1.1476</v>
+        <v>0.1951</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9435</v>
+        <v>2.2644</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.887</v>
+        <v>2.2644</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4825</v>
+        <v>0.3302</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0669</v>
+        <v>-0.0514</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4157</v>
+        <v>0.3816</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9813</v>
+        <v>-0.9624</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.9624</v>
       </c>
       <c r="X17" t="n">
-        <v>0.9813</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. LUENGO MATEO</t>
+          <t>V. SANTAMATILDE PERIS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.6451</v>
+        <v>3.7624</v>
       </c>
       <c r="E18" t="n">
-        <v>2.71</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9352</v>
+        <v>3.6774</v>
       </c>
       <c r="G18" t="n">
-        <v>2.4542</v>
+        <v>1.0913</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3827</v>
+        <v>-0.1471</v>
       </c>
       <c r="I18" t="n">
-        <v>2.0715</v>
+        <v>1.2384</v>
       </c>
       <c r="J18" t="n">
-        <v>3.8211</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>1.9447</v>
+        <v>0.8452</v>
       </c>
       <c r="L18" t="n">
-        <v>1.8764</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3669</v>
+        <v>0.1553</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.562</v>
+        <v>-0.9923</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1951</v>
+        <v>1.1476</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2644</v>
+        <v>0.9435</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2644</v>
+        <v>1.887</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1111</v>
+        <v>0.7463</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1488</v>
+        <v>0.0925</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0377</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9624</v>
+        <v>0.9813</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.9624</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.9813</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.0933</v>
+        <v>2.9791</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4118</v>
+        <v>0.5092</v>
       </c>
       <c r="F19" t="n">
-        <v>2.6816</v>
+        <v>2.4699</v>
       </c>
       <c r="G19" t="n">
         <v>1.1202</v>
@@ -1936,13 +1936,13 @@
         <v>1.5096</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7654</v>
+        <v>0.6512</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.291</v>
+        <v>-0.1936</v>
       </c>
       <c r="U19" t="n">
-        <v>1.0564</v>
+        <v>0.8448</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3018</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.5507</v>
+        <v>2.7217</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6863</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>3.2369</v>
+        <v>2.6285</v>
       </c>
       <c r="G20" t="n">
         <v>2.0186</v>
@@ -2014,13 +2014,13 @@
         <v>1.887</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5321</v>
+        <v>0.7030999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7984</v>
+        <v>-0.0189</v>
       </c>
       <c r="U20" t="n">
-        <v>1.3304</v>
+        <v>0.722</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.1337</v>
+        <v>0.9142</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.776</v>
+        <v>-1.3606</v>
       </c>
       <c r="F21" t="n">
-        <v>2.9097</v>
+        <v>2.2748</v>
       </c>
       <c r="G21" t="n">
         <v>0.7145</v>
@@ -2092,13 +2092,13 @@
         <v>1.887</v>
       </c>
       <c r="S21" t="n">
-        <v>2.061</v>
+        <v>0.8415</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7824</v>
+        <v>0.1978</v>
       </c>
       <c r="U21" t="n">
-        <v>1.2787</v>
+        <v>0.6438</v>
       </c>
       <c r="V21" t="n">
         <v>1.2452</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.7831</v>
+        <v>0.8793</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0618</v>
+        <v>-0.1331</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7214</v>
+        <v>1.0124</v>
       </c>
       <c r="G22" t="n">
         <v>1.6574</v>
@@ -2170,13 +2170,13 @@
         <v>2.4531</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1258</v>
+        <v>0.2219</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5472</v>
+        <v>0.3524</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4214</v>
+        <v>-0.1305</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6226</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2525</v>
+        <v>-0.368</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.4081</v>
+        <v>-2.6029</v>
       </c>
       <c r="F23" t="n">
-        <v>2.1556</v>
+        <v>2.235</v>
       </c>
       <c r="G23" t="n">
         <v>-1.5754</v>
@@ -2248,13 +2248,13 @@
         <v>1.6983</v>
       </c>
       <c r="S23" t="n">
-        <v>1.2098</v>
+        <v>1.0943</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5472</v>
+        <v>0.3524</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6626</v>
+        <v>0.7419</v>
       </c>
       <c r="V23" t="n">
         <v>0.3018</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.6325</v>
+        <v>-1.2344</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.4031</v>
+        <v>-2.1108</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7706</v>
+        <v>0.8764999999999999</v>
       </c>
       <c r="G24" t="n">
         <v>-1.059</v>
@@ -2326,13 +2326,13 @@
         <v>2.0757</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.743</v>
+        <v>-0.3449</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8107</v>
+        <v>-0.5184</v>
       </c>
       <c r="U24" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.1735</v>
       </c>
       <c r="V24" t="n">
         <v>1.8678</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>25.5818</v>
+        <v>25.5817</v>
       </c>
       <c r="E25" t="n">
         <v>4.243800000000002</v>
       </c>
       <c r="F25" t="n">
-        <v>21.3381</v>
+        <v>21.3383</v>
       </c>
       <c r="G25" t="n">
         <v>9.9938</v>
@@ -2404,13 +2404,13 @@
         <v>18.87</v>
       </c>
       <c r="S25" t="n">
-        <v>5.305499999999999</v>
+        <v>5.3054</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.01819999999999988</v>
+        <v>-0.01819999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>5.3237</v>
+        <v>5.323499999999999</v>
       </c>
       <c r="V25" t="n">
         <v>7.452100000000001</v>
